--- a/Cantera_ETC88.xlsx
+++ b/Cantera_ETC88.xlsx
@@ -1547,7 +1547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D39"/>
+  <dimension ref="A1:D38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1780,7 +1780,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Randol Joseph</t>
+          <t>Zahir Valoy</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1798,7 +1798,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Zahir Valoy</t>
+          <t>Enmanuel Mieses</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -1816,7 +1816,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Enmanuel Mieses</t>
+          <t>Neyrelis Santana</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1834,7 +1834,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Neyrelis Santana</t>
+          <t>Roselyn Quiroz</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -1852,7 +1852,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Roselyn Quiroz</t>
+          <t>Ganely</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -1870,7 +1870,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Ganely</t>
+          <t>Nelson Morales</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1888,7 +1888,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Nelson Morales</t>
+          <t>Inomar Mercedes</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1906,7 +1906,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Inomar Mercedes</t>
+          <t>Isaura Martinez</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1924,7 +1924,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Isaura Martinez</t>
+          <t>Avril Geronimo</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1942,7 +1942,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Avril Geronimo</t>
+          <t>Eduardo Candelario</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1950,17 +1950,21 @@
           <t>cocina</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr"/>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>guía ETC 78 y 79</t>
+        </is>
+      </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Padrino o participante</t>
+          <t>Auxiliar/Profondo (con experiencia)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Eduardo Candelario</t>
+          <t>Emilio Reyes</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1970,7 +1974,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>guía ETC 78 y 79</t>
+          <t>sirvió ETC 79</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -1982,7 +1986,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Emilio Reyes</t>
+          <t>Fabianlly</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1990,21 +1994,17 @@
           <t>cocina</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr">
-        <is>
-          <t>sirvió ETC 79</t>
-        </is>
-      </c>
+      <c r="C25" s="3" t="inlineStr"/>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar/Profondo (con experiencia)</t>
+          <t>Padrino o participante</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Fabianlly</t>
+          <t>Kirina Humpreys</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -2022,7 +2022,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>Kirina Humpreys</t>
+          <t>Leandro Fernandez</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -2030,17 +2030,21 @@
           <t>cocina</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr"/>
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>cocina ETC 85</t>
+        </is>
+      </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Padrino o participante</t>
+          <t>Auxiliar/Profondo (con experiencia)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Leandro Fernandez</t>
+          <t>Lucero Blanco</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -2048,21 +2052,17 @@
           <t>cocina</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr">
-        <is>
-          <t>cocina ETC 85</t>
-        </is>
-      </c>
+      <c r="C28" s="3" t="inlineStr"/>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar/Profondo (con experiencia)</t>
+          <t>Padrino o participante</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Lucero Blanco</t>
+          <t>Merkin Jean</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -2080,7 +2080,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Merkin Jean</t>
+          <t>Nestor Vidal</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -2088,17 +2088,21 @@
           <t>cocina</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr"/>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>cocina ETC 85</t>
+        </is>
+      </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Padrino o participante</t>
+          <t>Auxiliar/Profondo (con experiencia)</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Nestor Vidal</t>
+          <t>Rissel Santana</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -2106,21 +2110,17 @@
           <t>cocina</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
-        <is>
-          <t>cocina ETC 85</t>
-        </is>
-      </c>
+      <c r="C31" s="3" t="inlineStr"/>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar/Profondo (con experiencia)</t>
+          <t>Padrino o participante</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Rissel Santana</t>
+          <t>Rosanna Matos</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -2138,7 +2138,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Rosanna Matos</t>
+          <t>Vielimi Mena</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -2156,7 +2156,7 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Vielimi Mena</t>
+          <t>Yileivi Mena</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -2174,7 +2174,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Yileivi Mena</t>
+          <t>Daniel Santana (SD)</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -2192,7 +2192,7 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Daniel Santana (SD)</t>
+          <t>Mirna Stapleton (PC)</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -2210,7 +2210,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Mirna Stapleton (PC)</t>
+          <t>Ricaira Santana</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -2228,34 +2228,16 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>Ricaira Santana</t>
+          <t>Belkys</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>cocina</t>
+          <t>musica</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr"/>
       <c r="D38" s="3" t="inlineStr">
-        <is>
-          <t>Padrino o participante</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>Belkys</t>
-        </is>
-      </c>
-      <c r="B39" s="3" t="inlineStr">
-        <is>
-          <t>musica</t>
-        </is>
-      </c>
-      <c r="C39" s="3" t="inlineStr"/>
-      <c r="D39" s="3" t="inlineStr">
         <is>
           <t>Padrino o participante</t>
         </is>

--- a/Cantera_ETC88.xlsx
+++ b/Cantera_ETC88.xlsx
@@ -1547,7 +1547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D38"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -1780,7 +1780,7 @@
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
         <is>
-          <t>Zahir Valoy</t>
+          <t>Olanlly Ortiz</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1798,7 +1798,7 @@
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
         <is>
-          <t>Enmanuel Mieses</t>
+          <t>Zahir Valoy</t>
         </is>
       </c>
       <c r="B15" s="3" t="inlineStr">
@@ -1816,7 +1816,7 @@
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
         <is>
-          <t>Neyrelis Santana</t>
+          <t>Enmanuel Mieses</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1834,7 +1834,7 @@
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
         <is>
-          <t>Roselyn Quiroz</t>
+          <t>Neyrelis Santana</t>
         </is>
       </c>
       <c r="B17" s="3" t="inlineStr">
@@ -1852,7 +1852,7 @@
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
         <is>
-          <t>Ganely</t>
+          <t>Roselyn Quiroz</t>
         </is>
       </c>
       <c r="B18" s="3" t="inlineStr">
@@ -1870,7 +1870,7 @@
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
         <is>
-          <t>Nelson Morales</t>
+          <t>Ganely</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -1888,7 +1888,7 @@
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
         <is>
-          <t>Inomar Mercedes</t>
+          <t>Nelson Morales</t>
         </is>
       </c>
       <c r="B20" s="3" t="inlineStr">
@@ -1906,7 +1906,7 @@
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
         <is>
-          <t>Isaura Martinez</t>
+          <t>Inomar Mercedes</t>
         </is>
       </c>
       <c r="B21" s="3" t="inlineStr">
@@ -1924,7 +1924,7 @@
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>Avril Geronimo</t>
+          <t>Isaura Martinez</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
@@ -1942,7 +1942,7 @@
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>Eduardo Candelario</t>
+          <t>Avril Geronimo</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
@@ -1950,21 +1950,17 @@
           <t>cocina</t>
         </is>
       </c>
-      <c r="C23" s="3" t="inlineStr">
-        <is>
-          <t>guía ETC 78 y 79</t>
-        </is>
-      </c>
+      <c r="C23" s="3" t="inlineStr"/>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar/Profondo (con experiencia)</t>
+          <t>Padrino o participante</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Emilio Reyes</t>
+          <t>Eduardo Candelario</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1974,7 +1970,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>sirvió ETC 79</t>
+          <t>guía ETC 78 y 79</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -1986,7 +1982,7 @@
     <row r="25">
       <c r="A25" s="3" t="inlineStr">
         <is>
-          <t>Fabianlly</t>
+          <t>Emilio Reyes</t>
         </is>
       </c>
       <c r="B25" s="3" t="inlineStr">
@@ -1994,17 +1990,21 @@
           <t>cocina</t>
         </is>
       </c>
-      <c r="C25" s="3" t="inlineStr"/>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>sirvió ETC 79</t>
+        </is>
+      </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>Padrino o participante</t>
+          <t>Auxiliar/Profondo (con experiencia)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>Kirina Humpreys</t>
+          <t>Fabianlly</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
@@ -2022,7 +2022,7 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>Leandro Fernandez</t>
+          <t>Kirina Humpreys</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
@@ -2030,21 +2030,17 @@
           <t>cocina</t>
         </is>
       </c>
-      <c r="C27" s="3" t="inlineStr">
-        <is>
-          <t>cocina ETC 85</t>
-        </is>
-      </c>
+      <c r="C27" s="3" t="inlineStr"/>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar/Profondo (con experiencia)</t>
+          <t>Padrino o participante</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="inlineStr">
         <is>
-          <t>Lucero Blanco</t>
+          <t>Leandro Fernandez</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -2052,17 +2048,21 @@
           <t>cocina</t>
         </is>
       </c>
-      <c r="C28" s="3" t="inlineStr"/>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>cocina ETC 85</t>
+        </is>
+      </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>Padrino o participante</t>
+          <t>Auxiliar/Profondo (con experiencia)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
         <is>
-          <t>Merkin Jean</t>
+          <t>Lucero Blanco</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -2080,7 +2080,7 @@
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>Nestor Vidal</t>
+          <t>Merkin Jean</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
@@ -2088,21 +2088,17 @@
           <t>cocina</t>
         </is>
       </c>
-      <c r="C30" s="3" t="inlineStr">
-        <is>
-          <t>cocina ETC 85</t>
-        </is>
-      </c>
+      <c r="C30" s="3" t="inlineStr"/>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>Auxiliar/Profondo (con experiencia)</t>
+          <t>Padrino o participante</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>Rissel Santana</t>
+          <t>Nestor Vidal</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
@@ -2110,17 +2106,21 @@
           <t>cocina</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr"/>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>cocina ETC 85</t>
+        </is>
+      </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>Padrino o participante</t>
+          <t>Auxiliar/Profondo (con experiencia)</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>Rosanna Matos</t>
+          <t>Rissel Santana</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -2138,7 +2138,7 @@
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>Vielimi Mena</t>
+          <t>Rosanna Matos</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
@@ -2156,7 +2156,7 @@
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Yileivi Mena</t>
+          <t>Vielimi Mena</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -2174,7 +2174,7 @@
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Daniel Santana (SD)</t>
+          <t>Yileivi Mena</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
@@ -2192,7 +2192,7 @@
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Mirna Stapleton (PC)</t>
+          <t>Daniel Santana (SD)</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -2210,7 +2210,7 @@
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>Ricaira Santana</t>
+          <t>Mirna Stapleton (PC)</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -2228,16 +2228,34 @@
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>Belkys</t>
+          <t>Ricaira Santana</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>musica</t>
+          <t>cocina</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr"/>
       <c r="D38" s="3" t="inlineStr">
+        <is>
+          <t>Padrino o participante</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>Belkys</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="inlineStr">
+        <is>
+          <t>musica</t>
+        </is>
+      </c>
+      <c r="C39" s="3" t="inlineStr"/>
+      <c r="D39" s="3" t="inlineStr">
         <is>
           <t>Padrino o participante</t>
         </is>
